--- a/grupos/3APM - Estadisticos 20221.xlsx
+++ b/grupos/3APM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="123">
   <si>
     <t>Materia</t>
   </si>
@@ -167,10 +167,10 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
     <t>Ochoa Martínez Mayeli</t>
@@ -896,16 +896,16 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -938,7 +938,7 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -970,19 +970,19 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1018,7 +1018,7 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1047,16 +1047,16 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1083,16 +1083,16 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>6</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -1124,19 +1124,19 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1160,16 +1160,16 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>7</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1201,19 +1201,19 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1237,7 +1237,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1278,19 +1278,19 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1314,16 +1314,16 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1355,19 +1355,19 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1432,19 +1432,19 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1468,7 +1468,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1480,7 +1480,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1509,19 +1509,19 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1586,19 +1586,19 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1622,7 +1622,7 @@
         <v>9</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1663,16 +1663,16 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1702,13 +1702,13 @@
         <v>7</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>8</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1740,19 +1740,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1785,10 +1785,10 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1817,19 +1817,19 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1862,7 +1862,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -1894,19 +1894,19 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1942,7 +1942,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1971,19 +1971,19 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2019,7 +2019,7 @@
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2048,19 +2048,19 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2096,7 +2096,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2125,19 +2125,19 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2202,19 +2202,19 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2241,7 +2241,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2250,7 +2250,7 @@
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2279,19 +2279,19 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2315,7 +2315,7 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2327,7 +2327,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2356,19 +2356,19 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2404,7 +2404,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2433,19 +2433,19 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2472,16 +2472,16 @@
         <v>7</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>6</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2510,16 +2510,16 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2546,16 +2546,16 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>6</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2587,19 +2587,19 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2664,19 +2664,19 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2712,7 +2712,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2741,19 +2741,19 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2818,19 +2818,19 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2854,10 +2854,10 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>5</v>
@@ -2895,19 +2895,19 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2931,7 +2931,7 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -2940,7 +2940,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -3043,27 +3043,27 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>96.3</v>
       </c>
       <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
         <v>3.7</v>
-      </c>
-      <c r="H3">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -3072,25 +3072,25 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3740,7 +3740,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3787,7 +3787,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -3795,22 +3795,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920331</v>
+        <v>21330051920342</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3818,16 +3818,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920342</v>
+        <v>21330051920353</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -3836,29 +3836,6 @@
         <v>48</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920353</v>
-      </c>
-      <c r="B5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APM - Estadisticos 20221.xlsx
+++ b/grupos/3APM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="123">
   <si>
     <t>Materia</t>
   </si>
@@ -170,6 +170,9 @@
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
@@ -177,9 +180,6 @@
   </si>
   <si>
     <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
     <t>NC</t>
@@ -890,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -967,7 +967,7 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>8</v>
@@ -1003,7 +1003,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -1044,7 +1044,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -1059,7 +1059,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1095,7 +1095,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1121,7 +1121,7 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>8</v>
@@ -1157,7 +1157,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1198,7 +1198,7 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>7</v>
@@ -1275,7 +1275,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>7</v>
@@ -1311,7 +1311,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -1352,7 +1352,7 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>8</v>
@@ -1429,7 +1429,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
         <v>7</v>
@@ -1506,7 +1506,7 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>10</v>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <v>6</v>
@@ -1660,7 +1660,7 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
         <v>7</v>
@@ -1675,7 +1675,7 @@
         <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1737,7 +1737,7 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
         <v>8</v>
@@ -1814,7 +1814,7 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
         <v>7</v>
@@ -1891,7 +1891,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <v>8</v>
@@ -1927,7 +1927,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>9</v>
@@ -1968,7 +1968,7 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>9</v>
@@ -2004,7 +2004,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -2045,7 +2045,7 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
         <v>7</v>
@@ -2122,7 +2122,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>7</v>
@@ -2199,7 +2199,7 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
         <v>8</v>
@@ -2235,7 +2235,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2276,7 +2276,7 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
         <v>8</v>
@@ -2353,7 +2353,7 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
         <v>8</v>
@@ -2430,7 +2430,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>6</v>
@@ -2507,7 +2507,7 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
         <v>7</v>
@@ -2522,7 +2522,7 @@
         <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2543,7 +2543,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>8</v>
@@ -2584,7 +2584,7 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
         <v>9</v>
@@ -2661,7 +2661,7 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
         <v>9</v>
@@ -2738,7 +2738,7 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>9</v>
@@ -2774,7 +2774,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>9</v>
@@ -2815,7 +2815,7 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>6</v>
@@ -2892,7 +2892,7 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
         <v>10</v>
@@ -3063,7 +3063,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -3072,19 +3072,19 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3095,7 +3095,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3159,7 +3159,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3740,7 +3740,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3795,22 +3795,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920342</v>
+        <v>21330051920334</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3818,16 +3818,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920353</v>
+        <v>21330051920342</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -3836,6 +3836,29 @@
         <v>48</v>
       </c>
       <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920353</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APM - Estadisticos 20221.xlsx
+++ b/grupos/3APM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="123">
   <si>
     <t>Materia</t>
   </si>
@@ -899,7 +899,7 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -935,7 +935,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -976,7 +976,7 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -1053,7 +1053,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -1130,7 +1130,7 @@
         <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1207,7 +1207,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -1284,7 +1284,7 @@
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>7</v>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1438,7 +1438,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -1515,7 +1515,7 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -1592,7 +1592,7 @@
         <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -1669,7 +1669,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>7</v>
@@ -1705,7 +1705,7 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -1746,7 +1746,7 @@
         <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -1823,7 +1823,7 @@
         <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>9</v>
@@ -1859,7 +1859,7 @@
         <v>9</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -1900,7 +1900,7 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -1977,7 +1977,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -2013,7 +2013,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -2054,7 +2054,7 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>9</v>
@@ -2131,7 +2131,7 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -2208,7 +2208,7 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>9</v>
@@ -2285,7 +2285,7 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -2321,7 +2321,7 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2362,7 +2362,7 @@
         <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -2398,7 +2398,7 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2439,7 +2439,7 @@
         <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>5</v>
@@ -2516,7 +2516,7 @@
         <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
         <v>8</v>
@@ -2593,7 +2593,7 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>10</v>
@@ -2629,7 +2629,7 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2670,7 +2670,7 @@
         <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -2747,7 +2747,7 @@
         <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -2824,7 +2824,7 @@
         <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>7</v>
@@ -2901,7 +2901,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -3008,16 +3008,16 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="G2">
-        <v>7.41</v>
+        <v>3.7</v>
       </c>
       <c r="H2">
         <v>7.3</v>
@@ -3740,7 +3740,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3818,16 +3818,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920342</v>
+        <v>21330051920353</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -3836,29 +3836,6 @@
         <v>48</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920353</v>
-      </c>
-      <c r="B5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APM - Estadisticos 20221.xlsx
+++ b/grupos/3APM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="123">
   <si>
     <t>Materia</t>
   </si>
@@ -197,121 +197,121 @@
     <t>ABAD</t>
   </si>
   <si>
+    <t>AVELLEIRA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARAY</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>SOL</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
     <t>MARITZA</t>
-  </si>
-  <si>
-    <t>AVELLEIRA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARAY</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>SOL</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
   </si>
   <si>
     <t>ISRAEL</t>
@@ -875,7 +875,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -893,7 +893,7 @@
         <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>9</v>
@@ -929,7 +929,7 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -3043,22 +3043,22 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>96.3</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3196,7 +3196,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3221,26 +3221,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920331</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3282,13 +3262,13 @@
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3296,10 +3276,10 @@
         <v>21330051920332</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
         <v>98</v>
@@ -3313,10 +3293,10 @@
         <v>21330051920333</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
         <v>99</v>
@@ -3330,10 +3310,10 @@
         <v>21330051920334</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
         <v>100</v>
@@ -3347,10 +3327,10 @@
         <v>21330051920335</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
         <v>101</v>
@@ -3364,10 +3344,10 @@
         <v>21330051920137</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
         <v>102</v>
@@ -3381,10 +3361,10 @@
         <v>21330051920336</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
         <v>103</v>
@@ -3398,10 +3378,10 @@
         <v>21330051920338</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
         <v>104</v>
@@ -3415,10 +3395,10 @@
         <v>21330051920339</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
         <v>105</v>
@@ -3432,10 +3412,10 @@
         <v>21330051920340</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
         <v>106</v>
@@ -3449,10 +3429,10 @@
         <v>20330051920343</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
         <v>107</v>
@@ -3466,10 +3446,10 @@
         <v>21330051920341</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
         <v>108</v>
@@ -3483,10 +3463,10 @@
         <v>21330051920342</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
         <v>109</v>
@@ -3500,10 +3480,10 @@
         <v>21330051920343</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
         <v>110</v>
@@ -3517,10 +3497,10 @@
         <v>21330051920344</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
         <v>111</v>
@@ -3534,10 +3514,10 @@
         <v>21330051920345</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
         <v>112</v>
@@ -3551,10 +3531,10 @@
         <v>21330051920347</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
         <v>113</v>
@@ -3568,10 +3548,10 @@
         <v>21330051920348</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
         <v>114</v>
@@ -3585,10 +3565,10 @@
         <v>21330051920349</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
         <v>115</v>
@@ -3602,10 +3582,10 @@
         <v>21330051920350</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
         <v>116</v>
@@ -3619,10 +3599,10 @@
         <v>21330051920149</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
         <v>111</v>
@@ -3636,10 +3616,10 @@
         <v>21330051920351</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
         <v>117</v>
@@ -3653,10 +3633,10 @@
         <v>21330051920322</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
         <v>118</v>
@@ -3670,10 +3650,10 @@
         <v>21330051920174</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
         <v>119</v>
@@ -3687,10 +3667,10 @@
         <v>21330051920352</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s">
         <v>120</v>
@@ -3704,10 +3684,10 @@
         <v>21330051920353</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
         <v>121</v>
@@ -3721,10 +3701,10 @@
         <v>21330051920354</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D28" t="s">
         <v>122</v>
@@ -3778,10 +3758,10 @@
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -3790,7 +3770,7 @@
         <v>49</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3798,10 +3778,10 @@
         <v>21330051920334</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
         <v>100</v>
@@ -3821,10 +3801,10 @@
         <v>21330051920353</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
         <v>121</v>

--- a/grupos/3APM - Estadisticos 20221.xlsx
+++ b/grupos/3APM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="123">
   <si>
     <t>Materia</t>
   </si>
@@ -167,19 +167,19 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
   </si>
   <si>
     <t>NC</t>
@@ -908,10 +908,10 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -920,7 +920,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -929,7 +929,7 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -985,10 +985,10 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -997,7 +997,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1062,10 +1062,10 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1074,16 +1074,16 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1139,10 +1139,10 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1151,13 +1151,13 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1169,7 +1169,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1216,10 +1216,10 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1228,13 +1228,13 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>8</v>
@@ -1246,7 +1246,7 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1293,10 +1293,10 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1305,13 +1305,13 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -1323,7 +1323,7 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1370,10 +1370,10 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1382,7 +1382,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1400,7 +1400,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1447,10 +1447,10 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1459,13 +1459,13 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>8</v>
@@ -1524,10 +1524,10 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1536,7 +1536,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1554,7 +1554,7 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1601,10 +1601,10 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1613,7 +1613,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1622,7 +1622,7 @@
         <v>9</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1631,7 +1631,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1678,10 +1678,10 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1690,13 +1690,13 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>7</v>
@@ -1708,7 +1708,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1755,10 +1755,10 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1767,7 +1767,7 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1785,7 +1785,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1832,10 +1832,10 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1844,7 +1844,7 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1853,7 +1853,7 @@
         <v>8</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1862,7 +1862,7 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -1909,10 +1909,10 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1921,16 +1921,16 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -1986,10 +1986,10 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -1998,13 +1998,13 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -2063,10 +2063,10 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2075,7 +2075,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2084,7 +2084,7 @@
         <v>9</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>10</v>
@@ -2140,10 +2140,10 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2152,16 +2152,16 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2170,7 +2170,7 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2217,10 +2217,10 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2229,13 +2229,13 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2247,7 +2247,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2294,10 +2294,10 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2306,7 +2306,7 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2371,10 +2371,10 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2383,16 +2383,16 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2401,7 +2401,7 @@
         <v>7</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2448,10 +2448,10 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2460,16 +2460,16 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -2478,7 +2478,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2525,10 +2525,10 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2537,7 +2537,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2546,7 +2546,7 @@
         <v>9</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>9</v>
@@ -2602,10 +2602,10 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2614,7 +2614,7 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2679,10 +2679,10 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2691,16 +2691,16 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2709,7 +2709,7 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2756,10 +2756,10 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2768,7 +2768,7 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2833,10 +2833,10 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -2845,16 +2845,16 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2910,10 +2910,10 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -2922,7 +2922,7 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -2931,7 +2931,7 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -2940,7 +2940,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -3040,19 +3040,19 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="G3">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3063,7 +3063,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -3072,19 +3072,19 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3095,7 +3095,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3159,7 +3159,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3720,7 +3720,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3752,70 +3752,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920331</v>
+        <v>21330051920353</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920334</v>
-      </c>
-      <c r="B3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920353</v>
-      </c>
-      <c r="B4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APM - Estadisticos 20221.xlsx
+++ b/grupos/3APM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="123">
   <si>
     <t>Materia</t>
   </si>
@@ -917,7 +917,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>9</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>9</v>
@@ -1071,7 +1071,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
         <v>8</v>
@@ -1148,7 +1148,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
         <v>6</v>
@@ -1225,7 +1225,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>8</v>
@@ -1243,7 +1243,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1302,7 +1302,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
         <v>7</v>
@@ -1379,7 +1379,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
         <v>8</v>
@@ -1456,7 +1456,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>9</v>
@@ -1533,7 +1533,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>8</v>
@@ -1610,7 +1610,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>8</v>
@@ -1687,7 +1687,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>6</v>
@@ -1764,7 +1764,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>6</v>
@@ -1841,7 +1841,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>8</v>
@@ -1918,7 +1918,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>9</v>
@@ -1995,7 +1995,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>9</v>
@@ -2072,7 +2072,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>9</v>
@@ -2090,7 +2090,7 @@
         <v>10</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2149,7 +2149,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>6</v>
@@ -2226,7 +2226,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
         <v>6</v>
@@ -2303,7 +2303,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>9</v>
@@ -2321,7 +2321,7 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2380,7 +2380,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
         <v>6</v>
@@ -2457,7 +2457,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>7</v>
@@ -2475,7 +2475,7 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2534,7 +2534,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>9</v>
@@ -2552,7 +2552,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>9</v>
@@ -2611,7 +2611,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>9</v>
@@ -2629,7 +2629,7 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2688,7 +2688,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <v>8</v>
@@ -2706,7 +2706,7 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2765,7 +2765,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>9</v>
@@ -2842,7 +2842,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
         <v>6</v>
@@ -2860,7 +2860,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -2919,7 +2919,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>8</v>
@@ -3008,19 +3008,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3720,7 +3720,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3750,29 +3750,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920353</v>
-      </c>
-      <c r="B2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/3APM - Estadisticos 20221.xlsx
+++ b/grupos/3APM - Estadisticos 20221.xlsx
@@ -914,7 +914,7 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>8</v>
@@ -991,7 +991,7 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -1009,7 +1009,7 @@
         <v>8</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>9</v>
@@ -1068,7 +1068,7 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>6</v>
@@ -1145,7 +1145,7 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>8</v>
@@ -1163,7 +1163,7 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>7</v>
@@ -1222,7 +1222,7 @@
         <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>8</v>
@@ -1299,7 +1299,7 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>8</v>
@@ -1317,7 +1317,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1376,7 +1376,7 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>8</v>
@@ -1453,7 +1453,7 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>7</v>
@@ -1530,7 +1530,7 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -1607,7 +1607,7 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>8</v>
@@ -1684,7 +1684,7 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -1761,7 +1761,7 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>9</v>
@@ -1838,7 +1838,7 @@
         <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>7</v>
@@ -1915,7 +1915,7 @@
         <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>8</v>
@@ -1992,7 +1992,7 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -2069,7 +2069,7 @@
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
         <v>9</v>
@@ -2146,7 +2146,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>7</v>
@@ -2164,7 +2164,7 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2223,7 +2223,7 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -2300,7 +2300,7 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>7</v>
@@ -2377,7 +2377,7 @@
         <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>7</v>
@@ -2395,7 +2395,7 @@
         <v>8</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -2454,7 +2454,7 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>8</v>
@@ -2472,7 +2472,7 @@
         <v>6</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2531,7 +2531,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2608,7 +2608,7 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -2685,7 +2685,7 @@
         <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>9</v>
@@ -2762,7 +2762,7 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -2839,7 +2839,7 @@
         <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>7</v>
@@ -2857,7 +2857,7 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -2916,7 +2916,7 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>10</v>
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/grupos/3APM - Estadisticos 20221.xlsx
+++ b/grupos/3APM - Estadisticos 20221.xlsx
@@ -923,7 +923,7 @@
         <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1000,7 +1000,7 @@
         <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -1018,7 +1018,7 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1077,7 +1077,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>6</v>
@@ -1095,7 +1095,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1154,7 +1154,7 @@
         <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>6</v>
@@ -1231,7 +1231,7 @@
         <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -1249,7 +1249,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1308,7 +1308,7 @@
         <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1385,7 +1385,7 @@
         <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1462,7 +1462,7 @@
         <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1480,7 +1480,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1539,7 +1539,7 @@
         <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1557,7 +1557,7 @@
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1616,7 +1616,7 @@
         <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1693,7 +1693,7 @@
         <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>8</v>
@@ -1711,7 +1711,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1770,7 +1770,7 @@
         <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1788,7 +1788,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1847,7 +1847,7 @@
         <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -1924,7 +1924,7 @@
         <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -1942,7 +1942,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2001,7 +2001,7 @@
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -2078,7 +2078,7 @@
         <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -2096,7 +2096,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2155,7 +2155,7 @@
         <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2232,7 +2232,7 @@
         <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2309,7 +2309,7 @@
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2386,7 +2386,7 @@
         <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -2463,7 +2463,7 @@
         <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
         <v>6</v>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2617,7 +2617,7 @@
         <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2694,7 +2694,7 @@
         <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2771,7 +2771,7 @@
         <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2789,7 +2789,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2848,7 +2848,7 @@
         <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>6</v>
@@ -2866,7 +2866,7 @@
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2925,7 +2925,7 @@
         <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
